--- a/data/raw/건물토지매매.xlsx
+++ b/data/raw/건물토지매매.xlsx
@@ -10690,7 +10690,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">

--- a/data/raw/건물토지매매.xlsx
+++ b/data/raw/건물토지매매.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X154"/>
+  <dimension ref="A1:X155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,7 +616,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -714,7 +714,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2754,7 +2754,7 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4252,7 +4252,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -5176,7 +5176,7 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -7600,7 +7600,7 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>입55억, 2층3000/200,3층4000/150,4층2000/160,</t>
+          <t>입55억, 1층3000/280, 2층3000/200,3층4000/150,4층5000/140,5층6층2000/160, 관리비1-4층12만 5-6층 10만</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -8447,7 +8447,7 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -9457,7 +9457,7 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -9555,7 +9555,7 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -11646,11 +11646,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>ㅁ</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
           <t>250117</t>
@@ -11720,7 +11716,11 @@
       <c r="X119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ㅁ</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>250120</t>
@@ -12374,11 +12374,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>ㅁ</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
           <t>250208</t>
@@ -12435,7 +12431,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -12464,7 +12460,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ㅁ</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>250303</t>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -14233,61 +14233,85 @@
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>250908</t>
+        </is>
+      </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>청천동</t>
+          <t>청라동</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>142-3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>54500</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>230,000</t>
+          <t>185,000</t>
         </is>
       </c>
       <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>3.50%</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>4.08%</t>
+        </is>
+      </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>지하50, 1층 커피숍3000/250, 2층1000/150, 3층1000/80, 4층 주택 전세1억 원룸2개 월세50가능</t>
-        </is>
-      </c>
-      <c r="T150" t="inlineStr"/>
-      <c r="U150" t="inlineStr"/>
-      <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr"/>
-      <c r="X150" t="inlineStr"/>
+          <t xml:space="preserve">1층 1호 1000/90, 2호 1000/84, 3호~5호 각 1000/90, 2층 1호 전14000 2호 전18000 각 방3화2 3층전부+4층다락 전 16500 / 다락 방2화2, 몇 안되는 엘베있는 건물. 3층 천장쪽 판넬로 막음. 위반여지있음. </t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>생</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>소유주</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>본인</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>010-2588-6734</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
@@ -14327,7 +14351,7 @@
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
@@ -14352,16 +14376,20 @@
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>가좌동</t>
+          <t>청천동</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>212-4</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr">
         <is>
           <t>4</t>
@@ -14375,7 +14403,7 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>230,000</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
@@ -14392,86 +14420,90 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>130000까지</t>
-        </is>
-      </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>오</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>생</t>
-        </is>
-      </c>
+          <t>지하50, 1층 커피숍3000/250, 2층1000/150, 3층1000/80, 4층 주택 전세1억 원룸2개 월세50가능</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>임대인</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>010-4036-8150</t>
-        </is>
-      </c>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>가좌동</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>212-4</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
           <t>140,000</t>
         </is>
       </c>
       <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>4.03%</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr"/>
-      <c r="U153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>130000까지</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>오</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>생</t>
+        </is>
+      </c>
       <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
-      <c r="X153" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>임대인</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>010-4036-8150</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>부평동</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>633-8</t>
-        </is>
-      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
@@ -14479,35 +14511,85 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>3.50%</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>미래부동산 매물 손님 연력 해달라고 함</t>
-        </is>
-      </c>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" t="inlineStr"/>
-      <c r="X154" t="inlineStr">
+      <c r="X154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>부평동</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>633-8</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>미래부동산 매물 손님 연력 해달라고 함</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr">
         <is>
           <t>010-2355-6511</t>
         </is>

--- a/data/raw/건물토지매매.xlsx
+++ b/data/raw/건물토지매매.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X154"/>
+  <dimension ref="A1:X155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,7 +616,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -714,7 +714,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2754,7 +2754,7 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4252,7 +4252,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -5176,7 +5176,7 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -7600,7 +7600,7 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>입55억, 2층3000/200,3층4000/150,4층2000/160,</t>
+          <t>입55억, 1층3000/280, 2층3000/200,3층4000/150,4층5000/140,5층6층2000/160, 관리비1-4층12만 5-6층 10만</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -8447,7 +8447,7 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -9457,7 +9457,7 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -9555,7 +9555,7 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -11646,11 +11646,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>ㅁ</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
           <t>250117</t>
@@ -11720,7 +11716,11 @@
       <c r="X119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ㅁ</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>250120</t>
@@ -12374,11 +12374,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>ㅁ</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
           <t>250208</t>
@@ -12435,7 +12431,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -12464,7 +12460,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ㅁ</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>250303</t>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -14233,61 +14233,85 @@
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>250908</t>
+        </is>
+      </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>청천동</t>
+          <t>청라동</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>142-3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>54500</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>230,000</t>
+          <t>185,000</t>
         </is>
       </c>
       <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>3.50%</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>4.08%</t>
+        </is>
+      </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>지하50, 1층 커피숍3000/250, 2층1000/150, 3층1000/80, 4층 주택 전세1억 원룸2개 월세50가능</t>
-        </is>
-      </c>
-      <c r="T150" t="inlineStr"/>
-      <c r="U150" t="inlineStr"/>
-      <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr"/>
-      <c r="X150" t="inlineStr"/>
+          <t xml:space="preserve">1층 1호 1000/90, 2호 1000/84, 3호~5호 각 1000/90, 2층 1호 전14000 2호 전18000 각 방3화2 3층전부+4층다락 전 16500 / 다락 방2화2, 몇 안되는 엘베있는 건물. 3층 천장쪽 판넬로 막음. 위반여지있음. </t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>생</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>소유주</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>본인</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>010-2588-6734</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
@@ -14327,7 +14351,7 @@
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
@@ -14352,16 +14376,20 @@
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>가좌동</t>
+          <t>청천동</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>212-4</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr">
         <is>
           <t>4</t>
@@ -14375,7 +14403,7 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>230,000</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
@@ -14392,86 +14420,90 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>130000까지</t>
-        </is>
-      </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>오</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>생</t>
-        </is>
-      </c>
+          <t>지하50, 1층 커피숍3000/250, 2층1000/150, 3층1000/80, 4층 주택 전세1억 원룸2개 월세50가능</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>임대인</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>010-4036-8150</t>
-        </is>
-      </c>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>가좌동</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>212-4</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
           <t>140,000</t>
         </is>
       </c>
       <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>4.03%</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr"/>
-      <c r="U153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>130000까지</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>오</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>생</t>
+        </is>
+      </c>
       <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
-      <c r="X153" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>임대인</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>010-4036-8150</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>부평동</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>633-8</t>
-        </is>
-      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
@@ -14479,35 +14511,85 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>3.50%</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>미래부동산 매물 손님 연력 해달라고 함</t>
-        </is>
-      </c>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" t="inlineStr"/>
-      <c r="X154" t="inlineStr">
+      <c r="X154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>부평동</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>633-8</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>미래부동산 매물 손님 연력 해달라고 함</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr">
         <is>
           <t>010-2355-6511</t>
         </is>

--- a/data/raw/건물토지매매.xlsx
+++ b/data/raw/건물토지매매.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X155"/>
+  <dimension ref="A1:X166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -12460,11 +12460,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>ㅁ</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
           <t>250303</t>
@@ -12651,7 +12647,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -13359,7 +13355,11 @@
       <c r="X139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ㅁ</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>250613</t>
@@ -14315,15 +14315,19 @@
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>250909</t>
+        </is>
+      </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>청천동</t>
+          <t>석남동</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>480-8</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -14334,42 +14338,74 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>610.10</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>230.00</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>551.00</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>16000</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>230,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>3.50%</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>지하50, 1층 커피숍3000/250, 2층1000/150, 3층1000/80, 4층 주택 전세1억 원룸2개 월세50가능</t>
-        </is>
-      </c>
-      <c r="T151" t="inlineStr"/>
-      <c r="U151" t="inlineStr"/>
+          <t>28억입금, 평당1600정도,</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>오</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>생</t>
+        </is>
+      </c>
       <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr"/>
-      <c r="X151" t="inlineStr"/>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>임대인</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>010-3899-9834</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
@@ -14409,7 +14445,7 @@
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -14434,16 +14470,20 @@
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>가좌동</t>
+          <t>청천동</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>212-4</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G153" t="inlineStr">
         <is>
           <t>4</t>
@@ -14457,7 +14497,7 @@
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>230,000</t>
         </is>
       </c>
       <c r="O153" t="inlineStr"/>
@@ -14474,86 +14514,90 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>130000까지</t>
-        </is>
-      </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>오</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>생</t>
-        </is>
-      </c>
+          <t>지하50, 1층 커피숍3000/250, 2층1000/150, 3층1000/80, 4층 주택 전세1억 원룸2개 월세50가능</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>임대인</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>010-4036-8150</t>
-        </is>
-      </c>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>가좌동</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>212-4</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
           <t>140,000</t>
         </is>
       </c>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>4.03%</t>
-        </is>
-      </c>
-      <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr"/>
-      <c r="U154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>130000까지</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>오</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>생</t>
+        </is>
+      </c>
       <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr"/>
-      <c r="X154" t="inlineStr"/>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>임대인</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>010-4036-8150</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>부평동</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>633-8</t>
-        </is>
-      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
@@ -14563,33 +14607,327 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>130,000</t>
-        </is>
-      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>3.50%</t>
-        </is>
-      </c>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>미래부동산 매물 손님 연력 해달라고 함</t>
-        </is>
-      </c>
+      <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
       <c r="W155" t="inlineStr"/>
-      <c r="X155" t="inlineStr">
+      <c r="X155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
+      <c r="W159" t="inlineStr"/>
+      <c r="X159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
+      <c r="W160" t="inlineStr"/>
+      <c r="X160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+      <c r="W161" t="inlineStr"/>
+      <c r="X161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+      <c r="W162" t="inlineStr"/>
+      <c r="X162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
+      <c r="W163" t="inlineStr"/>
+      <c r="X163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
+      <c r="W164" t="inlineStr"/>
+      <c r="X164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
+      <c r="X165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>부평동</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>633-8</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>미래부동산 매물 손님 연력 해달라고 함</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
+      <c r="W166" t="inlineStr"/>
+      <c r="X166" t="inlineStr">
         <is>
           <t>010-2355-6511</t>
         </is>
